--- a/PQIR_DATA/Category Taxonomy.xlsx
+++ b/PQIR_DATA/Category Taxonomy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\24115\Desktop\寒假\SO论文\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54BB4A1-2A1D-4F6A-89F2-6610B4A45221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7265948B-82BF-4BFE-B3E1-165B6CE0BFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4C1FD426-2F55-4BD7-ABF2-D0FBA05A56B7}"/>
   </bookViews>
@@ -494,7 +494,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>T37 Search for public datasets to test a newly developed algorithm or system</t>
+    <t>C37 Search for public datasets to test a newly developed algorithm or system</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
